--- a/r5-aist-trustworthyai-main/StructureDefinition-ext-model-card.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ext-model-card.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,8 +75,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>A reference to the DocumentReference resource that acts as the Model Card, containing detailed
- documentation, intended purpose, and risk assessments.</t>
+    <t>A reference to the DocumentReference resource that acts as the Model Card, containing detailed documentation, intended purpose, and risk assessments.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ext-model-card.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ext-model-card.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>A reference to the DocumentReference resource that acts as the Model Card, containing detailed documentation, intended purpose, and risk assessments.</t>
+    <t>References the model card that documents the AI system's intended purpose, limitations, performance, risks, and other relevant technical information.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -322,7 +322,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference)
+    <t xml:space="preserve">Reference(http://example.org/fhir/eu-ai-transparency/StructureDefinition/eu-ai-model-card)
 </t>
   </si>
   <si>
@@ -652,7 +652,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="26.3046875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="72.89453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>79</v>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ext-model-card.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ext-model-card.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ext-model-card.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ext-model-card.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ext-model-card.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ext-model-card.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ext-model-card.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ext-model-card.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/fhir/eu-ai-transparency/StructureDefinition/ext-model-card</t>
+    <t>http://example.org/fhir/trust-ai-transparency/StructureDefinition/ext-model-card</t>
   </si>
   <si>
     <t>Version</t>
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>EU_AIModelCardLink</t>
+    <t>Trust_AIModelCardLink</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T08:39:53+00:00</t>
+    <t>2026-09-09T11:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -322,7 +322,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/fhir/eu-ai-transparency/StructureDefinition/eu-ai-model-card)
+    <t xml:space="preserve">Reference(http://example.org/fhir/trust-ai-transparency/StructureDefinition/trust-ai-model-card)
 </t>
   </si>
   <si>
@@ -652,7 +652,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="72.89453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="76.35546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
